--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16A.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="95">
   <si>
     <t>48964</t>
   </si>
@@ -142,16 +142,16 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>EB8EA0BBB6E91717A1A11BE6CEC2EF51</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>B34AF43626A74CDAFDF6F4C860EFDEDB</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>Confianza</t>
@@ -163,7 +163,7 @@
     <t>Ley Laboral de los Servidores Públicos del Estado de Tlaxcala y sus Municipios</t>
   </si>
   <si>
-    <t>31/12/2007</t>
+    <t>31/12/2021</t>
   </si>
   <si>
     <t>22/12/2021</t>
@@ -175,13 +175,13 @@
     <t>Subdirección Jurídica</t>
   </si>
   <si>
-    <t>12/01/2023</t>
+    <t>24/04/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>5244A7E1175E826448DF4BC57F54D863</t>
+    <t>56198692A3F112117ECB248855A06745</t>
   </si>
   <si>
     <t>Ley Federal</t>
@@ -190,19 +190,13 @@
     <t>Ley Federal del Trabajo</t>
   </si>
   <si>
-    <t>01/05/1970</t>
-  </si>
-  <si>
     <t>05/04/2022</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/LEY%20FEDERAL%20DEL%20TRAB.22.pdf</t>
   </si>
   <si>
-    <t>27/12/2022</t>
-  </si>
-  <si>
-    <t>193501402CEC13F90915490B71EF8B2E</t>
+    <t>7FB615A8F5E8FAAFEE2681AC73DA2BA8</t>
   </si>
   <si>
     <t>Base</t>
@@ -217,10 +211,10 @@
     <t>22/03/2019</t>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/condiciones%20generales%20de%20trabajo/</t>
-  </si>
-  <si>
-    <t>F1C73DAC1319F3E44E672126205DA433</t>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/condiciones%20generales%20de%20trabajo/COND%20GRALES%20DE%20TRAB%20STAI%2019-20%20(2).PDF</t>
+  </si>
+  <si>
+    <t>BA6E270802326E2F6F0042FD98460760</t>
   </si>
   <si>
     <t>Contrato</t>
@@ -706,7 +700,7 @@
   <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -715,7 +709,7 @@
     <col min="7" max="7" width="124.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="128.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="172.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
@@ -970,10 +964,10 @@
         <v>56</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>50</v>
@@ -982,7 +976,7 @@
         <v>51</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>52</v>
@@ -990,7 +984,7 @@
     </row>
     <row r="10" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>41</v>
@@ -1002,22 +996,22 @@
         <v>43</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>50</v>
@@ -1026,7 +1020,7 @@
         <v>51</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>52</v>
@@ -1034,7 +1028,7 @@
     </row>
     <row r="11" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>41</v>
@@ -1046,22 +1040,22 @@
         <v>43</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>50</v>
@@ -1070,7 +1064,7 @@
         <v>51</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>52</v>
@@ -1087,10 +1081,10 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E174">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F174">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F201">
       <formula1>Hidden_25</formula1>
     </dataValidation>
   </dataValidations>
@@ -1110,12 +1104,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1130,27 +1124,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -1160,7 +1154,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -1170,112 +1164,112 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
